--- a/Editor/Templates/ScriptTemplate.xlsx
+++ b/Editor/Templates/ScriptTemplate.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -35,11 +35,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>HeadProfile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>CharLeft</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>CharMid_Left</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>CharMid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharMid_Right</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -396,10 +408,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -432,6 +444,15 @@
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
